--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/CALIFORNIA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/CALIFORNIA_2013.xlsx
@@ -2227,7 +2227,7 @@
         <v>32</v>
       </c>
       <c r="D104">
-        <v>9.8557366547E-05</v>
+        <v>9.855736654700001E-05</v>
       </c>
     </row>
     <row r="105">
@@ -2695,7 +2695,7 @@
         <v>30</v>
       </c>
       <c r="D130">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="131">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C198">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C260">
@@ -5935,7 +5935,7 @@
         <v>30</v>
       </c>
       <c r="D310">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="311">
@@ -6277,7 +6277,7 @@
         <v>30</v>
       </c>
       <c r="D329">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="330">
@@ -6943,7 +6943,7 @@
         <v>323</v>
       </c>
       <c r="D366">
-        <v>0.000994813418585</v>
+        <v>0.0009948134185850002</v>
       </c>
     </row>
     <row r="367">
@@ -7015,7 +7015,7 @@
         <v>30</v>
       </c>
       <c r="D370">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="371">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C417">
@@ -8689,7 +8689,7 @@
         <v>315</v>
       </c>
       <c r="D463">
-        <v>0.000970174076949</v>
+        <v>0.0009701740769490002</v>
       </c>
     </row>
     <row r="464">
@@ -8743,7 +8743,7 @@
         <v>30</v>
       </c>
       <c r="D466">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="467">
@@ -9391,7 +9391,7 @@
         <v>320</v>
       </c>
       <c r="D502">
-        <v>0.000985573665472</v>
+        <v>0.0009855736654720002</v>
       </c>
     </row>
     <row r="503">
@@ -9607,7 +9607,7 @@
         <v>315</v>
       </c>
       <c r="D514">
-        <v>0.000970174076949</v>
+        <v>0.0009701740769490002</v>
       </c>
     </row>
     <row r="515">
@@ -10381,7 +10381,7 @@
         <v>30</v>
       </c>
       <c r="D557">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="558">
@@ -11281,7 +11281,7 @@
         <v>30</v>
       </c>
       <c r="D607">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="608">
@@ -13837,7 +13837,7 @@
         <v>3024</v>
       </c>
       <c r="D749">
-        <v>0.009313671138707</v>
+        <v>0.009313671138707002</v>
       </c>
     </row>
     <row r="750">
@@ -16890,7 +16890,7 @@
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C919">
@@ -18157,7 +18157,7 @@
         <v>30</v>
       </c>
       <c r="D989">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="990">
@@ -20191,7 +20191,7 @@
         <v>30</v>
       </c>
       <c r="D1102">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="1103">
@@ -20821,7 +20821,7 @@
         <v>32</v>
       </c>
       <c r="D1137">
-        <v>9.8557366547E-05</v>
+        <v>9.855736654700001E-05</v>
       </c>
     </row>
     <row r="1138">
@@ -20940,7 +20940,7 @@
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1144">
@@ -20958,7 +20958,7 @@
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1145">
@@ -22045,7 +22045,7 @@
         <v>30</v>
       </c>
       <c r="D1205">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="1206">
@@ -22099,7 +22099,7 @@
         <v>30</v>
       </c>
       <c r="D1208">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="1209">
@@ -22243,7 +22243,7 @@
         <v>30</v>
       </c>
       <c r="D1216">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="1217">
@@ -22740,7 +22740,7 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1244">
@@ -22758,7 +22758,7 @@
       </c>
       <c r="B1245" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1245">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1257">
@@ -26232,7 +26232,7 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1438">
@@ -26833,7 +26833,7 @@
         <v>32</v>
       </c>
       <c r="D1471">
-        <v>9.8557366547E-05</v>
+        <v>9.855736654700001E-05</v>
       </c>
     </row>
     <row r="1472">
@@ -27427,7 +27427,7 @@
         <v>30</v>
       </c>
       <c r="D1504">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="1505">
@@ -27499,7 +27499,7 @@
         <v>30</v>
       </c>
       <c r="D1508">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="1509">
@@ -28284,7 +28284,7 @@
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>General Felipe _Ngeles</t>
+          <t>General Felipe Angeles</t>
         </is>
       </c>
       <c r="C1552">
@@ -28327,7 +28327,7 @@
         <v>32</v>
       </c>
       <c r="D1554">
-        <v>9.8557366547E-05</v>
+        <v>9.855736654700001E-05</v>
       </c>
     </row>
     <row r="1555">
@@ -28741,7 +28741,7 @@
         <v>32</v>
       </c>
       <c r="D1577">
-        <v>9.8557366547E-05</v>
+        <v>9.855736654700001E-05</v>
       </c>
     </row>
     <row r="1578">
@@ -29101,7 +29101,7 @@
         <v>32</v>
       </c>
       <c r="D1597">
-        <v>9.8557366547E-05</v>
+        <v>9.855736654700001E-05</v>
       </c>
     </row>
     <row r="1598">
@@ -29371,7 +29371,7 @@
         <v>32</v>
       </c>
       <c r="D1612">
-        <v>9.8557366547E-05</v>
+        <v>9.855736654700001E-05</v>
       </c>
     </row>
     <row r="1613">
@@ -30307,7 +30307,7 @@
         <v>315</v>
       </c>
       <c r="D1664">
-        <v>0.000970174076949</v>
+        <v>0.0009701740769490002</v>
       </c>
     </row>
     <row r="1665">
@@ -31153,7 +31153,7 @@
         <v>32</v>
       </c>
       <c r="D1711">
-        <v>9.8557366547E-05</v>
+        <v>9.855736654700001E-05</v>
       </c>
     </row>
     <row r="1712">
@@ -34836,7 +34836,7 @@
       </c>
       <c r="B1916" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1916">
@@ -35131,7 +35131,7 @@
         <v>32</v>
       </c>
       <c r="D1932">
-        <v>9.8557366547E-05</v>
+        <v>9.855736654700001E-05</v>
       </c>
     </row>
     <row r="1933">
@@ -35293,7 +35293,7 @@
         <v>32</v>
       </c>
       <c r="D1941">
-        <v>9.8557366547E-05</v>
+        <v>9.855736654700001E-05</v>
       </c>
     </row>
     <row r="1942">
@@ -35563,7 +35563,7 @@
         <v>30</v>
       </c>
       <c r="D1956">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="1957">
@@ -35808,7 +35808,7 @@
       </c>
       <c r="B1970" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1970">
@@ -36103,7 +36103,7 @@
         <v>30</v>
       </c>
       <c r="D1986">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="1987">
@@ -37147,7 +37147,7 @@
         <v>30</v>
       </c>
       <c r="D2044">
-        <v>9.2397531138E-05</v>
+        <v>9.239753113800001E-05</v>
       </c>
     </row>
     <row r="2045">
@@ -39210,7 +39210,7 @@
       </c>
       <c r="B2159" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C2159">
@@ -41053,7 +41053,7 @@
         <v>32</v>
       </c>
       <c r="D2261">
-        <v>9.8557366547E-05</v>
+        <v>9.855736654700001E-05</v>
       </c>
     </row>
     <row r="2262">
@@ -41215,7 +41215,7 @@
         <v>32</v>
       </c>
       <c r="D2270">
-        <v>9.8557366547E-05</v>
+        <v>9.855736654700001E-05</v>
       </c>
     </row>
     <row r="2271">
